--- a/data/trans_orig/P1411-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1411-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de infarto de miocardio en 2012</t>
+          <t>Población con diagnóstico de infarto de miocardio en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,97 +731,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1074,97 +1074,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>685112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>687087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>610255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1295331</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1297342</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676584</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>704815</t>
+          <t>703692</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1384536</t>
+          <t>1384703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,47 +1775,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3423</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10134</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3423</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9097</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16486</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>603528</t>
+          <t>604999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613585</t>
+          <t>613482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,49 +1888,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>610841</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>604130</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>613199</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>610841</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>605167</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>613209</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1079</t>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1212394</t>
+          <t>1214217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1225383</t>
+          <t>1225552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13982</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36124</t>
+          <t>34475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401999</t>
+          <t>401736</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418270</t>
+          <t>419037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>433818</t>
+          <t>434550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445561</t>
+          <t>444738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>841105</t>
+          <t>842754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>861252</t>
+          <t>861487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24714</t>
+          <t>25013</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>15429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35641</t>
+          <t>35552</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285072</t>
+          <t>284773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>301384</t>
+          <t>301574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>338287</t>
+          <t>338325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>350043</t>
+          <t>350038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>628141</t>
+          <t>628230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>648802</t>
+          <t>648353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22716</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27795</t>
+          <t>27770</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38678</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67291</t>
+          <t>67228</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205574</t>
+          <t>203850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>227135</t>
+          <t>227006</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>360001</t>
+          <t>360026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>376130</t>
+          <t>376623</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>570356</t>
+          <t>570419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>598969</t>
+          <t>598836</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55533</t>
+          <t>54956</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92701</t>
+          <t>92074</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26645</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51613</t>
+          <t>52273</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88276</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>132212</t>
+          <t>132501</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3334078</t>
+          <t>3334705</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3371246</t>
+          <t>3371823</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3502303</t>
+          <t>3501643</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3527271</t>
+          <t>3526754</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6848482</t>
+          <t>6848193</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6890882</t>
+          <t>6892418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de infarto de miocardio en 2016</t>
+          <t>Población con diagnóstico de infarto de miocardio en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3710,97 +3710,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4088,62 +4088,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5431</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4851</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>586436</t>
+          <t>585323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1149189</t>
+          <t>1148609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663966</t>
+          <t>664521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656027</t>
+          <t>656843</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1324154</t>
+          <t>1323740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>628463</t>
+          <t>627883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641701</t>
+          <t>641729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639051</t>
+          <t>640068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648077</t>
+          <t>648103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1273799</t>
+          <t>1273140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1288505</t>
+          <t>1288046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24178</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25743</t>
+          <t>25918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>453740</t>
+          <t>453729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470170</t>
+          <t>469578</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>490708</t>
+          <t>489712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>949024</t>
+          <t>948849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>965302</t>
+          <t>965654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>14785</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34034</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>25653</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>26830</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52533</t>
+          <t>53232</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>300296</t>
+          <t>300175</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>320462</t>
+          <t>319545</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>352757</t>
+          <t>352109</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368543</t>
+          <t>368540</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>659559</t>
+          <t>658860</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>685532</t>
+          <t>685262</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28162</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36619</t>
+          <t>34345</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30819</t>
+          <t>30146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56273</t>
+          <t>55650</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228836</t>
+          <t>228443</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244034</t>
+          <t>243679</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>363550</t>
+          <t>365824</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386281</t>
+          <t>386784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>600894</t>
+          <t>601517</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>626348</t>
+          <t>627021</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51860</t>
+          <t>52334</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85225</t>
+          <t>84642</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32832</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60519</t>
+          <t>60112</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>92504</t>
+          <t>92978</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>136450</t>
+          <t>134252</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3309125</t>
+          <t>3309708</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3342490</t>
+          <t>3342016</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3484023</t>
+          <t>3484430</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3511710</t>
+          <t>3511946</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6802442</t>
+          <t>6804640</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6846388</t>
+          <t>6845914</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1411-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1411-Edad-trans_orig.xlsx
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>676702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>703692</t>
+          <t>704205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1384703</t>
+          <t>1385088</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>11967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604999</t>
+          <t>602650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613482</t>
+          <t>613481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>604130</t>
+          <t>605040</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1214217</t>
+          <t>1213527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1225552</t>
+          <t>1225460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>28092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>35701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401736</t>
+          <t>401337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>419037</t>
+          <t>418777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>434550</t>
+          <t>434167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>444738</t>
+          <t>445288</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>842754</t>
+          <t>841528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>861487</t>
+          <t>860720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25013</t>
+          <t>25176</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35552</t>
+          <t>34929</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284773</t>
+          <t>284610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>301574</t>
+          <t>301344</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>338325</t>
+          <t>338504</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>350038</t>
+          <t>350142</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>628230</t>
+          <t>628853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>648353</t>
+          <t>648686</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>23135</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>29112</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67228</t>
+          <t>68420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>203850</t>
+          <t>204831</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>227006</t>
+          <t>226716</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>360026</t>
+          <t>358684</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>376623</t>
+          <t>376725</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>570419</t>
+          <t>569227</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>598836</t>
+          <t>599173</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54956</t>
+          <t>55594</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>91189</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52273</t>
+          <t>51415</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88276</t>
+          <t>87559</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>132501</t>
+          <t>131258</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3334705</t>
+          <t>3335590</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3371823</t>
+          <t>3371185</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3501643</t>
+          <t>3502501</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3526754</t>
+          <t>3526995</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6848193</t>
+          <t>6849436</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6892418</t>
+          <t>6893135</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585323</t>
+          <t>585977</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1148609</t>
+          <t>1149531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664521</t>
+          <t>663985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656843</t>
+          <t>656725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1323740</t>
+          <t>1323675</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>21844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>627883</t>
+          <t>627810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641729</t>
+          <t>641891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640068</t>
+          <t>639277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648103</t>
+          <t>648087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1273140</t>
+          <t>1273281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1288046</t>
+          <t>1287876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24189</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25918</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>453729</t>
+          <t>454224</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>469578</t>
+          <t>470250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>489712</t>
+          <t>490688</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>948849</t>
+          <t>948790</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>965654</t>
+          <t>965108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34155</t>
+          <t>31708</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26830</t>
+          <t>26737</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53232</t>
+          <t>52627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>300175</t>
+          <t>302622</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>319545</t>
+          <t>320853</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>352109</t>
+          <t>352671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368540</t>
+          <t>369448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>658860</t>
+          <t>659465</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>685262</t>
+          <t>685355</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>12420</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28555</t>
+          <t>28223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34345</t>
+          <t>35341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30146</t>
+          <t>31421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55650</t>
+          <t>54849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228443</t>
+          <t>228775</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243679</t>
+          <t>244578</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>365824</t>
+          <t>364828</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386784</t>
+          <t>386537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>601517</t>
+          <t>602318</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>627021</t>
+          <t>625746</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52334</t>
+          <t>51236</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84642</t>
+          <t>84785</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32596</t>
+          <t>32583</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60112</t>
+          <t>60992</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>92978</t>
+          <t>90718</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>134252</t>
+          <t>133851</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3309708</t>
+          <t>3309565</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3342016</t>
+          <t>3343114</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3484430</t>
+          <t>3483550</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3511946</t>
+          <t>3511959</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6804640</t>
+          <t>6805041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6845914</t>
+          <t>6848174</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
